--- a/output/Hubei/咸宁市_news.xlsx
+++ b/output/Hubei/咸宁市_news.xlsx
@@ -522,18 +522,28 @@
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2023年咸宁市消费情况</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>市统计局</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>False</t>
@@ -545,13 +555,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="M2" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="N2" t="n">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -572,18 +582,28 @@
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2023年咸宁市投资情况</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>市统计局</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>False</t>
@@ -594,15 +614,9 @@
           <t>[None]</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>283</v>
-      </c>
-      <c r="M3" t="n">
-        <v>105</v>
-      </c>
-      <c r="N3" t="n">
-        <v>189</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>http://www.xianning.gov.cn/data/sjj/202304/t20230416_3040519.shtml</t>
@@ -622,18 +636,28 @@
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2023年咸宁市房地产情况</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>市住建局</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>False</t>
@@ -645,13 +669,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="M4" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N4" t="n">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -672,18 +696,28 @@
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2023年咸宁市规模以上工业运行情况</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>咸宁市统计局</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>False</t>
@@ -695,13 +729,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="M5" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N5" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -722,18 +756,28 @@
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>咸宁市二级运动员名单</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>市文化和旅游局</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2022-12-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>False</t>
@@ -745,13 +789,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="M6" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="N6" t="n">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -772,18 +816,28 @@
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>咸宁市12月气象信息</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>咸宁市气象台</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2022-12-15</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>False</t>
@@ -795,13 +849,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>362</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -822,18 +876,28 @@
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>咸宁市气象信息</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>咸宁市气象台</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2022-11-17</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>False</t>
@@ -845,13 +909,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -872,18 +936,28 @@
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>咸宁市气象信息</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>咸宁市气象台</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2022-11-17</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>False</t>
@@ -895,13 +969,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="M9" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="N9" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -922,18 +996,28 @@
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>咸宁市气象信息</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>咸宁市气象台</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2022-11-17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>False</t>
@@ -945,13 +1029,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="M10" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N10" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -972,18 +1056,28 @@
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2022年咸宁市投资情况</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>咸宁市统计局</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>False</t>
@@ -995,13 +1089,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="M11" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="N11" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1022,18 +1116,28 @@
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2022年咸宁市消费情况</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>咸宁市统计局</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2022-11-14</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>False</t>
@@ -1044,15 +1148,9 @@
           <t>[None]</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>409</v>
-      </c>
-      <c r="M12" t="n">
-        <v>152</v>
-      </c>
-      <c r="N12" t="n">
-        <v>273</v>
-      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>http://www.xianning.gov.cn/data/sjj/202211/t20221114_2841955.shtml</t>
@@ -1072,18 +1170,28 @@
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2022年咸宁市规模以上工业运行情况</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>咸宁市统计局</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2022-11-14</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1094,14 +1202,12 @@
           <t>[None]</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>414</v>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="N13" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1122,18 +1228,28 @@
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>咸宁市气象信息</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>咸宁市气象台</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2022-11-14</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1144,14 +1260,12 @@
           <t>[None]</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="N14" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1172,18 +1286,28 @@
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>咸宁市气象灾害预警信号</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>咸宁市气象台</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2022-11-14</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>False</t>
@@ -1195,13 +1319,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1222,18 +1346,28 @@
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>咸宁市2022年房地产市场运行情况</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>咸宁市住房和城乡建设局</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2022-11-14</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1244,15 +1378,9 @@
           <t>[None]</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>389</v>
-      </c>
-      <c r="M16" t="n">
-        <v>145</v>
-      </c>
-      <c r="N16" t="n">
-        <v>260</v>
-      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>http://www.xianning.gov.cn/data/sjj/202211/t20221114_2841838.shtml</t>
@@ -1272,18 +1400,28 @@
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>咸宁市气象灾害预警信号</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>市气象局</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2021-12-28</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>False</t>
@@ -1295,13 +1433,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="M17" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N17" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1322,18 +1460,28 @@
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>咸宁市专题气象信息</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>市气象局</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2021-12-28</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>False</t>
@@ -1345,13 +1493,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="M18" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N18" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1372,18 +1520,28 @@
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>规模以上工业生产增长情况</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>市统计局</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2021-12-28</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>False</t>
@@ -1394,14 +1552,10 @@
           <t>[None]</t>
         </is>
       </c>
-      <c r="L19" t="n">
-        <v>531</v>
-      </c>
-      <c r="M19" t="n">
-        <v>197</v>
-      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1422,18 +1576,28 @@
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>咸宁市主要经济指标</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>市统计局</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2021-12-28</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>False</t>
@@ -1445,13 +1609,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="M20" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="N20" t="n">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1472,18 +1636,28 @@
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>咸宁市城区房地产市场运行情况</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>市住建局</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2021-12-27</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>False</t>
@@ -1495,13 +1669,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="M21" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N21" t="n">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1522,18 +1696,28 @@
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>咸宁市旅游业数据接口</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>市文化和旅游局</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2021-12-28</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>True</t>
@@ -1544,14 +1728,10 @@
           <t>[None]</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>611</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1572,18 +1752,28 @@
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>咸宁市财政总收入数据接口</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>市统计局</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2021-12-28</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>True</t>
@@ -1594,14 +1784,10 @@
           <t>[None]</t>
         </is>
       </c>
-      <c r="L23" t="n">
-        <v>242</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1622,18 +1808,28 @@
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>咸宁市GDP数据接口</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>市统计局</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2021-12-28</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>True</t>
@@ -1645,13 +1841,11 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>415</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1672,18 +1866,28 @@
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>咸宁市社会消费品零售总额数据接口</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>市统计局</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2021-12-28</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>True</t>
@@ -1695,13 +1899,11 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>148</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
